--- a/workspaces/traject_224/input_v3_in_use.xlsx
+++ b/workspaces/traject_224/input_v3_in_use.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CP\git_clones\GeoProb-Pipe\GeoProb-PipeV2\GeoProb-Pipe\workspaces\traject_224\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsrlnl-my.sharepoint.com/personal/a_methorst_wsrl_nl/Documents/Bureaublad/GeoProb-Clones/GeoProb-PipeV1/GeoProb-Pipe/workspaces/traject_224/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDA4D74-A1BF-4397-B5C5-7B5340BC9C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView minimized="1" xWindow="62280" yWindow="4665" windowWidth="17250" windowHeight="8865" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
